--- a/docs/design/2026-09-10-relic-redesign/GameXXK_遗物设计总表_2026-09-10.xlsx
+++ b/docs/design/2026-09-10-relic-redesign/GameXXK_遗物设计总表_2026-09-10.xlsx
@@ -496,7 +496,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>16普通/特殊 + 20稀有 + 10史诗；高品质是本轮候选，尚未接入旧31件运行时。设计、实现与验证分开记录。</t>
+          <t>16普通/特殊 + 20稀有 + 10史诗；30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过。完整实牌和平衡验收未完成。</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>本轮相邻回归待执行</t>
+          <t>普通防护/回复相邻回归通过；完整验收待完成</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -702,12 +702,12 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>本轮相邻回归待执行</t>
+          <t>普通防护/回复相邻回归通过；完整验收待完成</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N6" s="5" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>本轮相邻回归待执行</t>
+          <t>普通防护/回复相邻回归通过；完整验收待完成</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>本轮相邻回归待执行</t>
+          <t>普通防护/回复相邻回归通过；完整验收待完成</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>本轮相邻回归待执行</t>
+          <t>普通防护/回复相邻回归通过；完整验收待完成</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>本轮相邻回归待执行</t>
+          <t>普通防护/回复相邻回归通过；完整验收待完成</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>本轮相邻回归待执行</t>
+          <t>普通防护/回复相邻回归通过；完整验收待完成</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>本轮相邻回归待执行</t>
+          <t>普通防护/回复相邻回归通过；完整验收待完成</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N12" s="5" t="inlineStr">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>本轮相邻回归待执行</t>
+          <t>普通防护/回复相邻回归通过；完整验收待完成</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1278,12 +1278,12 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>本轮相邻回归待执行</t>
+          <t>普通防护/回复相邻回归通过；完整验收待完成</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>本轮相邻回归待执行</t>
+          <t>普通防护/回复相邻回归通过；完整验收待完成</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>本轮相邻回归待执行</t>
+          <t>普通防护/回复相邻回归通过；完整验收待完成</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>本轮相邻回归待执行</t>
+          <t>普通防护/回复相邻回归通过；完整验收待完成</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>本轮相邻回归待执行</t>
+          <t>普通防护/回复相邻回归通过；完整验收待完成</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>本轮相邻回归待执行</t>
+          <t>普通防护/回复相邻回归通过；完整验收待完成</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>本轮相邻回归待执行</t>
+          <t>普通防护/回复相邻回归通过；完整验收待完成</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
@@ -1769,17 +1769,17 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
@@ -1905,17 +1905,17 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -1973,17 +1973,17 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
@@ -2041,17 +2041,17 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2109,17 +2109,17 @@
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
@@ -2177,17 +2177,17 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2245,17 +2245,17 @@
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
@@ -2313,17 +2313,17 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -2381,17 +2381,17 @@
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
@@ -2449,20 +2449,24 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>重绘待完成</t>
-        </is>
-      </c>
-      <c r="N31" s="4" t="inlineStr"/>
+          <t>已导入，重启加载通过</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_BloodInkSeal.png</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="60" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
@@ -2513,20 +2517,24 @@
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>重绘待完成</t>
-        </is>
-      </c>
-      <c r="N32" s="5" t="inlineStr"/>
+          <t>已导入，重启加载通过</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_StormChime.png</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="60" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
@@ -2577,20 +2585,24 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>重绘待完成</t>
-        </is>
-      </c>
-      <c r="N33" s="4" t="inlineStr"/>
+          <t>已导入，重启加载通过</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_FlameCenser.png</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="60" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
@@ -2641,20 +2653,24 @@
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>重绘待完成</t>
-        </is>
-      </c>
-      <c r="N34" s="5" t="inlineStr"/>
+          <t>已导入，重启加载通过</t>
+        </is>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_HunterQuiver.png</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="60" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
@@ -2705,20 +2721,24 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>重绘待完成</t>
-        </is>
-      </c>
-      <c r="N35" s="4" t="inlineStr"/>
+          <t>已导入，重启加载通过</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_MoonDewVial.png</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="60" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
@@ -2769,20 +2789,24 @@
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>重绘待完成</t>
-        </is>
-      </c>
-      <c r="N36" s="5" t="inlineStr"/>
+          <t>已导入，重启加载通过</t>
+        </is>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_WarBanner.png</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="60" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
@@ -2833,20 +2857,24 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>重绘待完成</t>
-        </is>
-      </c>
-      <c r="N37" s="4" t="inlineStr"/>
+          <t>已导入，重启加载通过</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_AmberPestle.png</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="60" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
@@ -2897,20 +2925,24 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>重绘待完成</t>
-        </is>
-      </c>
-      <c r="N38" s="5" t="inlineStr"/>
+          <t>已导入，重启加载通过</t>
+        </is>
+      </c>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_TwinJade.png</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="60" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
@@ -2961,20 +2993,24 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>重绘待完成</t>
-        </is>
-      </c>
-      <c r="N39" s="4" t="inlineStr"/>
+          <t>已导入，重启加载通过</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_SilkFan.png</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="60" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
@@ -3025,20 +3061,24 @@
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>重绘待完成</t>
-        </is>
-      </c>
-      <c r="N40" s="5" t="inlineStr"/>
+          <t>已导入，重启加载通过</t>
+        </is>
+      </c>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_ObsidianScale.png</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="60" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
@@ -3089,17 +3129,17 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -3157,17 +3197,17 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr">
@@ -3225,17 +3265,17 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -3293,17 +3333,17 @@
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N44" s="5" t="inlineStr">
@@ -3361,17 +3401,17 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>已整理，未导入</t>
+          <t>已导入，重启加载通过</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -3429,20 +3469,24 @@
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>重绘待完成</t>
-        </is>
-      </c>
-      <c r="N46" s="5" t="inlineStr"/>
+          <t>已导入，重启加载通过</t>
+        </is>
+      </c>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_BloodMoonBlade.png</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="60" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
@@ -3493,20 +3537,24 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>重绘待完成</t>
-        </is>
-      </c>
-      <c r="N47" s="4" t="inlineStr"/>
+          <t>已导入，重启加载通过</t>
+        </is>
+      </c>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_PhoenixCauldron.png</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="60" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
@@ -3557,20 +3605,24 @@
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>重绘待完成</t>
-        </is>
-      </c>
-      <c r="N48" s="5" t="inlineStr"/>
+          <t>已导入，重启加载通过</t>
+        </is>
+      </c>
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_StarAbacus.png</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="60" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
@@ -3621,20 +3673,24 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>重绘待完成</t>
-        </is>
-      </c>
-      <c r="N49" s="4" t="inlineStr"/>
+          <t>已导入，重启加载通过</t>
+        </is>
+      </c>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_DragonCarapace.png</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="60" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
@@ -3685,20 +3741,24 @@
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>独立定义已编译；效果未接入</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>新机制回归待执行</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>重绘待完成</t>
-        </is>
-      </c>
-      <c r="N50" s="5" t="inlineStr"/>
+          <t>已导入，重启加载通过</t>
+        </is>
+      </c>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_ThunderSeal.png</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:N50"/>
